--- a/survey_templates/040_user_satisfaction_analysis_report_form--survey_templates.xlsx
+++ b/survey_templates/040_user_satisfaction_analysis_report_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Select One</t>
+          <t>Select One 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
+          <t>Select Multiple 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>Decimal 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>Integer 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Date and Time</t>
+          <t>Date Time 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Text Area</t>
+          <t>Text Area 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>checkbox_2</t>
+          <t>checkbox_2_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Checkbox 2 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Submit 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1330,7 +1330,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>checkbox_2_choices</t>
+          <t>checkbox_2_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>checkbox_2_choices</t>
+          <t>checkbox_2_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
